--- a/outputs/AmEx_Analytics_Dashboard.xlsx
+++ b/outputs/AmEx_Analytics_Dashboard.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fraud</t>
   </si>
   <si>
-    <t xml:space="preserve">Healthcare and Jewellery merchant categories show the highest fraud rates; the model catches most fraud value at a tuned threshold with very few false alarms on the test set.</t>
+    <t xml:space="preserve">Fraud rate is similar across merchant categories (about 1.0-1.4%), so category alone is a weak signal; fraud concentrates at 1-4 AM and in high-amount, far-from-home transactions, and the model catches most fraud value at a tuned threshold on the test set.</t>
   </si>
   <si>
     <t xml:space="preserve">Churn Risk</t>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">Business Recommendation</t>
   </si>
   <si>
-    <t xml:space="preserve">Deploy the fraud model at the tuned threshold for real-time transaction scoring on Healthcare and Jewellery categories first, where fraud rates are highest. Launch a retention program for the flagged churn-risk customers (priority to Platinum/Centurion tiers given their high lifetime value) - even a partial save-rate protects meaningful annual interchange/interest revenue from this cohort.</t>
+    <t xml:space="preserve">Deploy the fraud model at the tuned threshold for real-time transaction scoring, with step-up verification for late-night, high-amount and far-from-home transactions, the strongest fraud signals. Launch a retention program for the flagged churn-risk customers (priority to Platinum/Centurion tiers given their high lifetime value) - even a partial save-rate protects meaningful annual interchange/interest revenue from this cohort.</t>
   </si>
   <si>
     <t xml:space="preserve">Supporting Data (referenced by formulas on other sheets)</t>
@@ -5244,11 +5244,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="60513847"/>
-        <c:axId val="88537085"/>
+        <c:axId val="85685887"/>
+        <c:axId val="76638036"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="60513847"/>
+        <c:axId val="85685887"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5280,7 +5280,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="88537085"/>
+        <c:crossAx val="76638036"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5288,7 +5288,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="88537085"/>
+        <c:axId val="76638036"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5330,7 +5330,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="60513847"/>
+        <c:crossAx val="85685887"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5555,11 +5555,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="99404504"/>
-        <c:axId val="48712600"/>
+        <c:axId val="41220692"/>
+        <c:axId val="72597037"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="99404504"/>
+        <c:axId val="41220692"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5591,7 +5591,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48712600"/>
+        <c:crossAx val="72597037"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5599,7 +5599,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="48712600"/>
+        <c:axId val="72597037"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5641,7 +5641,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99404504"/>
+        <c:crossAx val="41220692"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
